--- a/research/traditional_assets/database/data/isle_of_man/isle_of_man_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/isle_of_man/isle_of_man_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.067</v>
+        <v>0.3674999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.05330162283156128</v>
+        <v>0.04002169197396963</v>
       </c>
       <c r="H2">
-        <v>-0.05330162283156128</v>
+        <v>0.04002169197396963</v>
       </c>
       <c r="I2">
-        <v>-0.6456351426972581</v>
+        <v>0.04750542299349241</v>
       </c>
       <c r="J2">
-        <v>-0.6456351426972581</v>
+        <v>0.04402335010391705</v>
       </c>
       <c r="K2">
-        <v>-4.981</v>
+        <v>10.256</v>
       </c>
       <c r="L2">
-        <v>-0.2322794254803209</v>
+        <v>1.11236442516269</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>90.32000000000001</v>
+        <v>39.77</v>
       </c>
       <c r="V2">
-        <v>0.176766342373233</v>
+        <v>0.2807029926595144</v>
       </c>
       <c r="W2">
-        <v>-0.2552531380753138</v>
+        <v>0.0412307052252744</v>
       </c>
       <c r="X2">
-        <v>0.04817272237335087</v>
+        <v>0.07972813541093351</v>
       </c>
       <c r="Y2">
-        <v>-0.3034258604486647</v>
+        <v>-0.03849743018565912</v>
       </c>
       <c r="Z2">
-        <v>0.5921139827700463</v>
+        <v>0.1636986666193207</v>
       </c>
       <c r="AA2">
-        <v>-0.6627388881671576</v>
+        <v>0.04082735666375908</v>
       </c>
       <c r="AB2">
-        <v>0.04817272237335087</v>
+        <v>0.07923716956192145</v>
       </c>
       <c r="AC2">
-        <v>-0.7113680078112899</v>
+        <v>-0.03840981289816236</v>
       </c>
       <c r="AD2">
-        <v>0.11</v>
+        <v>0.195</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.11</v>
+        <v>0.195</v>
       </c>
       <c r="AG2">
-        <v>-90.21000000000001</v>
+        <v>-39.575</v>
       </c>
       <c r="AH2">
-        <v>0.0002152359671041175</v>
+        <v>0.001374449339207049</v>
       </c>
       <c r="AI2">
-        <v>0.0003754650646823906</v>
+        <v>0.001071399137386336</v>
       </c>
       <c r="AJ2">
-        <v>-0.2144043807798987</v>
+        <v>-0.387591205131972</v>
       </c>
       <c r="AK2">
-        <v>-0.4451517394522576</v>
+        <v>-0.2782367209196049</v>
       </c>
       <c r="AL2">
-        <v>0.038</v>
+        <v>0.016</v>
       </c>
       <c r="AM2">
-        <v>-0.172</v>
+        <v>-0.409</v>
       </c>
       <c r="AN2">
-        <v>-0.728476821192053</v>
+        <v>0.4721549636803875</v>
       </c>
       <c r="AO2">
-        <v>-364.3421052631579</v>
+        <v>27.375</v>
       </c>
       <c r="AP2">
-        <v>597.4172185430464</v>
+        <v>-95.82324455205813</v>
       </c>
       <c r="AQ2">
-        <v>80.49418604651164</v>
+        <v>-1.070904645476773</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Agronomics Limited (AIM:ANIC)</t>
+          <t>Cambria Africa plc (AIM:CMB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,23 +715,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.306</v>
+      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.2617021276595745</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.2617021276595745</v>
       </c>
       <c r="I3">
-        <v>0.2306122448979592</v>
+        <v>0.2914893617021276</v>
       </c>
       <c r="J3">
-        <v>0.2306122448979592</v>
+        <v>0.2487579369499833</v>
       </c>
       <c r="K3">
-        <v>1.41</v>
+        <v>0.056</v>
       </c>
       <c r="L3">
-        <v>0.09591836734693877</v>
+        <v>0.03971631205673759</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,64 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>86.2</v>
+        <v>1.57</v>
       </c>
       <c r="V3">
-        <v>0.3016095171448566</v>
+        <v>0.564748201438849</v>
       </c>
       <c r="W3">
-        <v>0.05875</v>
+        <v>0.008655332302936631</v>
       </c>
       <c r="X3">
-        <v>0.04817272237335087</v>
+        <v>0.08111492714075665</v>
       </c>
       <c r="Y3">
-        <v>0.01057727762664912</v>
+        <v>-0.07245959483782001</v>
       </c>
       <c r="Z3">
-        <v>0.7153284671532846</v>
+        <v>0.3261623872310895</v>
       </c>
       <c r="AA3">
-        <v>0.164963503649635</v>
+        <v>0.0811354825582874</v>
       </c>
       <c r="AB3">
-        <v>0.04817272237335087</v>
+        <v>0.08013299544273249</v>
       </c>
       <c r="AC3">
-        <v>0.1167907812762841</v>
+        <v>0.001002487115554909</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="AG3">
-        <v>-86.2</v>
+        <v>-1.375</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.06554621848739497</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.02744546094299789</v>
       </c>
       <c r="AJ3">
-        <v>-0.4318637274549098</v>
+        <v>-0.9786476868327404</v>
       </c>
       <c r="AK3">
-        <v>-1.657692307692308</v>
+        <v>-0.2484191508581752</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="AM3">
-        <v>-0.207</v>
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="AN3">
+        <v>0.4721549636803875</v>
+      </c>
+      <c r="AO3">
+        <v>25.6875</v>
+      </c>
+      <c r="AP3">
+        <v>-3.329297820823245</v>
       </c>
       <c r="AQ3">
-        <v>-16.3768115942029</v>
+        <v>45.66666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cambria Africa plc (AIM:CMB)</t>
+          <t>Agronomics Limited (AIM:ANIC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,25 +844,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.429</v>
+        <v>1.041</v>
       </c>
       <c r="G4">
-        <v>0.2912801484230055</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.2912801484230055</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.5473098330241186</v>
+        <v>0.003457106274007683</v>
       </c>
       <c r="J4">
-        <v>-0.5473098330241186</v>
+        <v>0.003457106274007683</v>
       </c>
       <c r="K4">
-        <v>-0.441</v>
+        <v>10.2</v>
       </c>
       <c r="L4">
-        <v>-0.8181818181818181</v>
+        <v>1.306017925736236</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -859,7 +871,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -868,311 +880,70 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.54</v>
+        <v>38.2</v>
       </c>
       <c r="V4">
-        <v>0.7475728155339806</v>
+        <v>0.2750179985601152</v>
       </c>
       <c r="W4">
-        <v>-0.06150627615062761</v>
+        <v>0.07380607814761216</v>
       </c>
       <c r="X4">
-        <v>0.04993874152920941</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="Y4">
-        <v>-0.111445017679837</v>
+        <v>-0.004535265533498242</v>
       </c>
       <c r="Z4">
-        <v>0.1154422788605697</v>
+        <v>0.1501923076923077</v>
       </c>
       <c r="AA4">
-        <v>-0.06318269436710215</v>
+        <v>0.0005192307692307693</v>
       </c>
       <c r="AB4">
-        <v>0.04908551691491374</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AC4">
-        <v>-0.1122682112820159</v>
+        <v>-0.07782211291187963</v>
       </c>
       <c r="AD4">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-1.43</v>
+        <v>-38.2</v>
       </c>
       <c r="AH4">
-        <v>0.05069124423963134</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.01553672316384181</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-2.269841269841269</v>
+        <v>-0.3793445878848064</v>
       </c>
       <c r="AK4">
-        <v>-0.2581227436823105</v>
+        <v>-0.2794440380395026</v>
       </c>
       <c r="AL4">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.037</v>
-      </c>
-      <c r="AN4">
-        <v>-0.728476821192053</v>
-      </c>
-      <c r="AO4">
-        <v>-7.763157894736842</v>
-      </c>
-      <c r="AP4">
-        <v>9.470198675496688</v>
+        <v>-0.418</v>
       </c>
       <c r="AQ4">
-        <v>-7.972972972972973</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Isle of Man</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Origo Partners PLC (AIM:OPP)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>1.614906832298137</v>
-      </c>
-      <c r="H5">
-        <v>1.614906832298137</v>
-      </c>
-      <c r="I5">
-        <v>1.913043478260869</v>
-      </c>
-      <c r="J5">
-        <v>1.913043478260869</v>
-      </c>
-      <c r="K5">
-        <v>-1.46</v>
-      </c>
-      <c r="L5">
-        <v>1.813664596273292</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>1.38</v>
-      </c>
-      <c r="V5">
-        <v>1.979913916786227</v>
-      </c>
-      <c r="W5">
-        <v>-0.4694533762057878</v>
-      </c>
-      <c r="X5">
-        <v>0.04817272237335087</v>
-      </c>
-      <c r="Y5">
-        <v>-0.5176260985791387</v>
-      </c>
-      <c r="Z5">
-        <v>-0.6598360655737705</v>
-      </c>
-      <c r="AA5">
-        <v>-1.262295081967213</v>
-      </c>
-      <c r="AB5">
-        <v>0.04817272237335087</v>
-      </c>
-      <c r="AC5">
-        <v>-1.310467804340564</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>-1.38</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>2.020497803806735</v>
-      </c>
-      <c r="AK5">
-        <v>-4.451612903225805</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>-0.002</v>
-      </c>
-      <c r="AQ5">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Isle of Man</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>KR1 Plc (LSE:0A9X)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>2.563</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>-2.196861626248217</v>
-      </c>
-      <c r="J6">
-        <v>-2.196861626248217</v>
-      </c>
-      <c r="K6">
-        <v>-4.49</v>
-      </c>
-      <c r="L6">
-        <v>-0.6405135520684737</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>1.2</v>
-      </c>
-      <c r="V6">
-        <v>0.005395683453237409</v>
-      </c>
-      <c r="W6">
-        <v>-0.449</v>
-      </c>
-      <c r="X6">
-        <v>0.04817272237335087</v>
-      </c>
-      <c r="Y6">
-        <v>-0.4971727223733509</v>
-      </c>
-      <c r="Z6">
-        <v>0.7169888513859057</v>
-      </c>
-      <c r="AA6">
-        <v>-1.575125294057482</v>
-      </c>
-      <c r="AB6">
-        <v>0.04817272237335087</v>
-      </c>
-      <c r="AC6">
-        <v>-1.623298016430833</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>-1.2</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.005424954792043399</v>
-      </c>
-      <c r="AK6">
-        <v>-0.008287292817679558</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
+        <v>-0.0645933014354067</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/isle_of_man/isle_of_man_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/isle_of_man/isle_of_man_investments_asset_management.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3674999999999999</v>
+        <v>-0.404</v>
       </c>
       <c r="G2">
-        <v>0.04002169197396963</v>
+        <v>0.01027459775210577</v>
       </c>
       <c r="H2">
-        <v>0.04002169197396963</v>
+        <v>0.01027459775210577</v>
       </c>
       <c r="I2">
-        <v>0.04750542299349241</v>
+        <v>0.8193861319008006</v>
       </c>
       <c r="J2">
-        <v>0.04402335010391705</v>
+        <v>0.6145395989256004</v>
       </c>
       <c r="K2">
-        <v>10.256</v>
+        <v>28.204</v>
       </c>
       <c r="L2">
-        <v>1.11236442516269</v>
+        <v>0.7354943020314496</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>39.77</v>
+        <v>24.36</v>
       </c>
       <c r="V2">
-        <v>0.2807029926595144</v>
+        <v>0.1996394033764957</v>
       </c>
       <c r="W2">
-        <v>0.0412307052252744</v>
+        <v>0.06565834767252104</v>
       </c>
       <c r="X2">
-        <v>0.07972813541093351</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y2">
-        <v>-0.03849743018565912</v>
+        <v>-0.001130179677890766</v>
       </c>
       <c r="Z2">
-        <v>0.1636986666193207</v>
+        <v>0.2721227948168439</v>
       </c>
       <c r="AA2">
-        <v>0.04082735666375908</v>
+        <v>0.1272171326217836</v>
       </c>
       <c r="AB2">
-        <v>0.07923716956192145</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AC2">
-        <v>-0.03840981289816236</v>
+        <v>0.06042860527137179</v>
       </c>
       <c r="AD2">
-        <v>0.195</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.195</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-39.575</v>
+        <v>-24.36</v>
       </c>
       <c r="AH2">
-        <v>0.001374449339207049</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.001071399137386336</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.387591205131972</v>
+        <v>-0.2494368216260496</v>
       </c>
       <c r="AK2">
-        <v>-0.2782367209196049</v>
+        <v>-0.1244762391415432</v>
       </c>
       <c r="AL2">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.409</v>
-      </c>
-      <c r="AN2">
-        <v>0.4721549636803875</v>
-      </c>
-      <c r="AO2">
-        <v>27.375</v>
-      </c>
-      <c r="AP2">
-        <v>-95.82324455205813</v>
+        <v>-1.507</v>
       </c>
       <c r="AQ2">
-        <v>-1.070904645476773</v>
+        <v>-20.85003317850033</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cambria Africa plc (AIM:CMB)</t>
+          <t>Agronomics Limited (AIM:ANIC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,26 +706,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.306</v>
-      </c>
       <c r="G3">
-        <v>0.2617021276595745</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.2617021276595745</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.2914893617021276</v>
+        <v>0.8275862068965516</v>
       </c>
       <c r="J3">
-        <v>0.2487579369499833</v>
+        <v>0.8275862068965516</v>
       </c>
       <c r="K3">
-        <v>0.056</v>
+        <v>28.4</v>
       </c>
       <c r="L3">
-        <v>0.03971631205673759</v>
+        <v>0.7533156498673739</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +746,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.57</v>
+        <v>23</v>
       </c>
       <c r="V3">
-        <v>0.564748201438849</v>
+        <v>0.1907131011608624</v>
       </c>
       <c r="W3">
-        <v>0.008655332302936631</v>
+        <v>0.1623785020011435</v>
       </c>
       <c r="X3">
-        <v>0.08111492714075665</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y3">
-        <v>-0.07245959483782001</v>
+        <v>0.0955899746507317</v>
       </c>
       <c r="Z3">
-        <v>0.3261623872310895</v>
+        <v>0.2757863935625458</v>
       </c>
       <c r="AA3">
-        <v>0.0811354825582874</v>
+        <v>0.2282370153621068</v>
       </c>
       <c r="AB3">
-        <v>0.08013299544273249</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AC3">
-        <v>0.001002487115554909</v>
+        <v>0.161448488011695</v>
       </c>
       <c r="AD3">
-        <v>0.195</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.195</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.375</v>
+        <v>-23</v>
       </c>
       <c r="AH3">
-        <v>0.06554621848739497</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.02744546094299789</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.9786476868327404</v>
+        <v>-0.235655737704918</v>
       </c>
       <c r="AK3">
-        <v>-0.2484191508581752</v>
+        <v>-0.120545073375262</v>
       </c>
       <c r="AL3">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="AN3">
-        <v>0.4721549636803875</v>
-      </c>
-      <c r="AO3">
-        <v>25.6875</v>
-      </c>
-      <c r="AP3">
-        <v>-3.329297820823245</v>
+        <v>-1.49</v>
       </c>
       <c r="AQ3">
-        <v>45.66666666666666</v>
+        <v>-20.93959731543624</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +814,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agronomics Limited (AIM:ANIC)</t>
+          <t>Cambria Africa Plc (AIM:CMB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,25 +823,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>1.041</v>
+        <v>-0.404</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.6089644513137558</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.6089644513137558</v>
       </c>
       <c r="I4">
-        <v>0.003457106274007683</v>
+        <v>0.3415765069551777</v>
       </c>
       <c r="J4">
-        <v>0.003457106274007683</v>
+        <v>0.1707882534775889</v>
       </c>
       <c r="K4">
-        <v>10.2</v>
+        <v>-0.196</v>
       </c>
       <c r="L4">
-        <v>1.306017925736236</v>
+        <v>-0.3029366306027821</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -871,7 +850,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -880,37 +859,37 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>38.2</v>
+        <v>1.36</v>
       </c>
       <c r="V4">
-        <v>0.2750179985601152</v>
+        <v>0.9577464788732396</v>
       </c>
       <c r="W4">
-        <v>0.07380607814761216</v>
+        <v>-0.03106180665610143</v>
       </c>
       <c r="X4">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y4">
-        <v>-0.004535265533498242</v>
+        <v>-0.09785033400651325</v>
       </c>
       <c r="Z4">
-        <v>0.1501923076923077</v>
+        <v>0.1533902323376008</v>
       </c>
       <c r="AA4">
-        <v>0.0005192307692307693</v>
+        <v>0.02619724988146041</v>
       </c>
       <c r="AB4">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AC4">
-        <v>-0.07782211291187963</v>
+        <v>-0.0405912774689514</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -922,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-38.2</v>
+        <v>-1.36</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -931,19 +910,19 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.3793445878848064</v>
+        <v>-22.66666666666673</v>
       </c>
       <c r="AK4">
-        <v>-0.2794440380395026</v>
+        <v>-0.2775510204081633</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.418</v>
+        <v>-0.017</v>
       </c>
       <c r="AQ4">
-        <v>-0.0645933014354067</v>
+        <v>-13</v>
       </c>
     </row>
   </sheetData>
